--- a/Accounts 2026/Shareholders 2026/01 Shareholders/01 COCO COHEN New Worksheet 2026.xlsx
+++ b/Accounts 2026/Shareholders 2026/01 Shareholders/01 COCO COHEN New Worksheet 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrisa\Dropbox\Andrisa\Landco\Accounts 2026\Shareholders 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\landco\Accounts 2026\Shareholders 2026\01 Shareholders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CB7327-92AE-4512-96D2-7DBBB084E684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE867AF5-659A-4A5A-9FB8-BAA86B1C6777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{7530348A-2D9B-D147-BBFE-7340475C451A}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{7530348A-2D9B-D147-BBFE-7340475C451A}"/>
   </bookViews>
   <sheets>
     <sheet name="LANDCO" sheetId="6" r:id="rId1"/>
@@ -495,6 +495,7 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1598,6 +1599,9 @@
     <xf numFmtId="16" fontId="39" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1617,9 +1621,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
@@ -1785,7 +1786,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INCOME"/>
@@ -1795,11 +1795,17 @@
       <sheetName val="MONTHLY FOR THE YEAR"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0">
+        <row r="51">
+          <cell r="D51">
+            <v>812375</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="C4">
-            <v>-456526.24419999961</v>
+            <v>-456526.24425000005</v>
           </cell>
           <cell r="D4">
             <v>812375</v>
@@ -1855,7 +1861,13 @@
         </row>
       </sheetData>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="3">
+        <row r="6">
+          <cell r="D6">
+            <v>38090</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
@@ -1887,9 +1899,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2256,13 +2268,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="16" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="287" t="s">
+      <c r="A1" s="288" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="288"/>
-      <c r="C1" s="288"/>
-      <c r="D1" s="288"/>
-      <c r="E1" s="288"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
     </row>
     <row r="2" spans="1:12" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="63"/>
@@ -2289,9 +2301,9 @@
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="291"/>
-      <c r="K3" s="292"/>
-      <c r="L3" s="292"/>
+      <c r="J3" s="292"/>
+      <c r="K3" s="293"/>
+      <c r="L3" s="293"/>
     </row>
     <row r="4" spans="1:12" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
@@ -2299,7 +2311,7 @@
       </c>
       <c r="B4" s="66">
         <f>+[1]RECON!$C$4</f>
-        <v>-456526.24419999961</v>
+        <v>-456526.24425000005</v>
       </c>
       <c r="C4" s="66">
         <f>+[1]RECON!$D$4</f>
@@ -2311,7 +2323,7 @@
       </c>
       <c r="E4" s="66">
         <f>+B4+C4-D4</f>
-        <v>172438.58330000041</v>
+        <v>172438.58324999997</v>
       </c>
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
@@ -2434,7 +2446,7 @@
       </c>
       <c r="B9" s="74">
         <f>SUM(B4:B7)</f>
-        <v>603979.4833000002</v>
+        <v>603979.48324999982</v>
       </c>
       <c r="C9" s="74">
         <f>SUM(C4:C7)</f>
@@ -2446,7 +2458,7 @@
       </c>
       <c r="E9" s="74">
         <f>SUM(E4:E8)</f>
-        <v>1750481.3133000003</v>
+        <v>1750481.3132499999</v>
       </c>
       <c r="F9" s="76"/>
       <c r="G9" s="76"/>
@@ -2469,8 +2481,8 @@
       <c r="L10" s="237"/>
     </row>
     <row r="11" spans="1:12" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="289"/>
-      <c r="B11" s="290"/>
+      <c r="A11" s="290"/>
+      <c r="B11" s="291"/>
       <c r="C11" s="81"/>
       <c r="D11" s="81"/>
       <c r="E11" s="81"/>
@@ -2691,14 +2703,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="16" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="287" t="s">
+      <c r="A1" s="288" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="288"/>
-      <c r="C1" s="288"/>
-      <c r="D1" s="288"/>
-      <c r="E1" s="288"/>
-      <c r="F1" s="293"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="294"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="86"/>
@@ -2975,11 +2987,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="16" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="294" t="s">
+      <c r="A1" s="287" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="294"/>
-      <c r="C1" s="294"/>
+      <c r="B1" s="287"/>
+      <c r="C1" s="287"/>
     </row>
     <row r="2" spans="1:23" s="190" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="105" t="s">
@@ -27952,11 +27964,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="294" t="s">
+      <c r="A1" s="287" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="294"/>
-      <c r="C1" s="294"/>
+      <c r="B1" s="287"/>
+      <c r="C1" s="287"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
@@ -27964,11 +27976,11 @@
       <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" s="16" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="294" t="s">
+      <c r="A2" s="287" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="294"/>
-      <c r="C2" s="294"/>
+      <c r="B2" s="287"/>
+      <c r="C2" s="287"/>
     </row>
     <row r="3" spans="1:8" s="16" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="100"/>
